--- a/financas_casa.xlsx
+++ b/financas_casa.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,12 @@
       <color rgb="00E2E8F0"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000FF88"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="0016213E"/>
         <bgColor rgb="0016213E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F3460"/>
+        <bgColor rgb="000F3460"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,6 +116,14 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -483,6 +501,7 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -529,6 +548,11 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Comprovante</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Recorrente</t>
         </is>
       </c>
     </row>
@@ -543,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -557,6 +581,13 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -615,6 +646,41 @@
           <t>Comprovante</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Num Parcelas</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Parcela Atual</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Dia Vencimento</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Data Vencimento</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Status Pagamento</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Total (R$)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Parcela (R$)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -667,6 +733,1227 @@
         <is>
           <t>Compra_Eletrodomesticos_Geladeira_2026-03-06_09-32-31.pdf</t>
         </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>2352.02</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2352.02</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Jogo de panela</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>sam's club</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>399.91</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Compra a vista</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Compra_Cozinha_Jogo_de_panela_2026-03-12_15-28-13.jpeg</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>399.91</v>
+      </c>
+      <c r="R3" t="n">
+        <v>399.91</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Tabua de carne</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>59.97</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Pago a vista no pix</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Compra_Cozinha_Tabua_de_carne_2026-03-12_22-13-06.jpeg</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>59.97</v>
+      </c>
+      <c r="R4" t="n">
+        <v>59.97</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Faqueiro</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>62.81</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>A vista no pix</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Compra_Cozinha_Faqueiro_2026-03-12_22-20-40.jpeg</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>62.81</v>
+      </c>
+      <c r="R5" t="n">
+        <v>62.81</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Jogo de jantar</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Ferreira costa</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>pago a vista no pix</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>89.90000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>2027-02-23</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>174.83</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +1967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -693,6 +1980,7 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -744,6 +2032,58 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Comprovante</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Recorrente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>tim- will</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>📱 Telefone</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Eu</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>conta de telefone tim</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -758,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -769,6 +2109,14 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -810,6 +2158,46 @@
       <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Observacao</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Total (R$)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Parcela (R$)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Num Parcelas</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Parcela Atual</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Dia Vencimento</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Data Vencimento</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Status Pagamento</t>
         </is>
       </c>
     </row>
@@ -824,7 +2212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -890,30 +2278,523 @@
       <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="n"/>
+      <c r="E3" s="6" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>837.3200000000001</v>
+      </c>
+      <c r="D28" t="n">
+        <v>787.4200000000001</v>
+      </c>
+      <c r="E28" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-837.3200000000001</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D29" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D30" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D31" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D32" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D33" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D34" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D35" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D36" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D37" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D38" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D39" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
         <v>2352.02</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D40" t="n">
         <v>2352.02</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
         <v>-2352.02</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>

--- a/financas_casa.xlsx
+++ b/financas_casa.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -553,6 +553,138 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Recorrente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>pagamento dia 16</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>💼 Salário</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Eu</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>700</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Pagamento da ultimate academy</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>pagamento dia 1</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>💼 Salário</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Eu</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Pagamento da ultimate academy</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>pagamento Rematec</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>💼 Salário</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Eu</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>800</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>pagamento da rematec</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -684,26 +816,26 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Geladeira</t>
+          <t>Jogo de panela</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>🏠 Eletrodomésticos</t>
+          <t>🍳 Cozinha</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Casa baiha</t>
+          <t>sam's club</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -712,7 +844,7 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2352.02</v>
+        <v>399.91</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -721,17 +853,17 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Média</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Comprado a vista</t>
+          <t>Compra a vista</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Compra_Eletrodomesticos_Geladeira_2026-03-06_09-32-31.pdf</t>
+          <t>Compra_Cozinha_Jogo_de_panela_2026-03-12_15-28-13.jpeg</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -743,79 +875,79 @@
       <c r="N2" t="n">
         <v>10</v>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Pago</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
-        <v>2352.02</v>
+        <v>399.91</v>
       </c>
       <c r="R2" t="n">
-        <v>2352.02</v>
+        <v>399.91</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Jogo de panela</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Tabua de carne</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>🍳 Cozinha</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>sam's club</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>399.91</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="n">
+        <v>59.97</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Compra a vista</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Compra_Cozinha_Jogo_de_panela_2026-03-12_15-28-13.jpeg</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Pago a vista no pix</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Compra_Cozinha_Tabua_de_carne_2026-03-12_22-13-06.jpeg</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="5" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
@@ -832,68 +964,68 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>399.91</v>
+        <v>59.97</v>
       </c>
       <c r="R3" t="n">
-        <v>399.91</v>
+        <v>59.97</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Tabua de carne</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="A4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Faqueiro</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>🍳 Cozinha</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Shopee</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>59.97</v>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="n">
+        <v>62.81</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Pago a vista no pix</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Compra_Cozinha_Tabua_de_carne_2026-03-12_22-13-06.jpeg</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>A vista no pix</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Compra_Cozinha_Faqueiro_2026-03-12_22-20-40.jpeg</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="M4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="n">
@@ -910,68 +1042,64 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>59.97</v>
+        <v>62.81</v>
       </c>
       <c r="R4" t="n">
-        <v>59.97</v>
+        <v>62.81</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Faqueiro</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Jogo de jantar</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>🍳 Cozinha</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Ferreira costa</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>62.81</v>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="6" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>A vista no pix</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Compra_Cozinha_Faqueiro_2026-03-12_22-20-40.jpeg</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="n">
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>pago a vista no pix</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="5" t="n">
         <v>1</v>
       </c>
       <c r="N5" t="n">
@@ -988,34 +1116,34 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>62.81</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>62.81</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Jogo de jantar</t>
+          <t>Ar condicionado</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>🍳 Cozinha</t>
+          <t>🏠 Eletrodomésticos</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Ferreira costa</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1024,876 +1152,876 @@
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>89.90000000000001</v>
+        <v>2098</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Comprado</t>
+          <t>Parcelado</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>pago a vista no pix</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Pago</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="R6" t="n">
-        <v>89.90000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Ar condicionado</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M12" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="N12" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>2098</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Ar condicionado</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>🏠 Eletrodomésticos</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="G13" s="4" t="n">
         <v>2098</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Parcelado</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="5" t="n">
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="5" t="n">
+      <c r="M13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="Q13" s="4" t="n">
         <v>2098</v>
       </c>
-      <c r="R7" s="6" t="n">
-        <v>174.83</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="R13" s="4" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Ar condicionado</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>🏠 Eletrodomésticos</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G14" s="6" t="n">
         <v>2098</v>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Parcelado</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="n">
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="M14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N14" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="Q14" s="6" t="n">
         <v>2098</v>
       </c>
-      <c r="R8" s="4" t="n">
-        <v>174.83</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Ar condicionado</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>🏠 Eletrodomésticos</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G15" s="4" t="n">
         <v>2098</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Parcelado</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="5" t="n">
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="5" t="n">
+      <c r="M15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="Q15" s="4" t="n">
         <v>2098</v>
       </c>
-      <c r="R9" s="6" t="n">
-        <v>174.83</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="R15" s="4" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Ar condicionado</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>🏠 Eletrodomésticos</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G16" s="6" t="n">
         <v>2098</v>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Parcelado</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="n">
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="N10" s="3" t="n">
+      <c r="M16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="N16" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>2027-01-23</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="Q16" s="6" t="n">
         <v>2098</v>
       </c>
-      <c r="R10" s="4" t="n">
-        <v>174.83</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v>174.83</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Ar condicionado</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>🏠 Eletrodomésticos</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G17" s="4" t="n">
         <v>2098</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Parcelado</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="n">
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="M11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N11" s="5" t="n">
+      <c r="M17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="N17" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>2027-02-23</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q17" s="4" t="n">
         <v>2098</v>
       </c>
-      <c r="R11" s="6" t="n">
-        <v>174.83</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Ar condicionado</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>🏠 Eletrodomésticos</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>2098</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Parcelado</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>2098</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>174.83</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Ar condicionado</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>🏠 Eletrodomésticos</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>2098</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Parcelado</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>2098</v>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v>174.83</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Ar condicionado</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>🏠 Eletrodomésticos</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>2098</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>Parcelado</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="n">
-        <v>2098</v>
-      </c>
-      <c r="R14" s="4" t="n">
-        <v>174.83</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Ar condicionado</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>🏠 Eletrodomésticos</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>2098</v>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Parcelado</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>2098</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>174.83</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Ar condicionado</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>🏠 Eletrodomésticos</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>2098</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Parcelado</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>2026-12-23</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="n">
-        <v>2098</v>
-      </c>
-      <c r="R16" s="4" t="n">
-        <v>174.83</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Ar condicionado</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>🏠 Eletrodomésticos</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Ambos</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>2098</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>Parcelado</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr"/>
-      <c r="L17" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>2027-01-23</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>2098</v>
-      </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="4" t="n">
         <v>174.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Ar condicionado</t>
+          <t>Geladeira</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1903,7 +2031,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Casa baiha</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1912,11 +2040,11 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2098</v>
+        <v>2352.02</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Parcelado</t>
+          <t>Comprado</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1926,34 +2054,34 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Comprado a vista</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr"/>
       <c r="L18" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>2027-02-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>2098</v>
+        <v>2352.02</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>174.83</v>
+        <v>2352.02</v>
       </c>
     </row>
   </sheetData>
@@ -2058,7 +2186,7 @@
         <v>49.9</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -2072,7 +2200,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>03/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -2212,7 +2340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2410,391 +2538,452 @@
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>837.3200000000001</v>
-      </c>
-      <c r="D28" t="n">
-        <v>787.4200000000001</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="B119" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C119" t="n">
+        <v>3139.44</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3139.44</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-1639.44</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>700</v>
+      </c>
+      <c r="C120" t="n">
+        <v>224.73</v>
+      </c>
+      <c r="D120" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E120" t="n">
         <v>49.9</v>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-837.3200000000001</v>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>475.27</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D121" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H121" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D29" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D122" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D30" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D123" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D31" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D124" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D32" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D125" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D33" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D126" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D34" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D127" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D35" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D128" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D36" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D129" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D37" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D130" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D38" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D39" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Pago</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2352.02</v>
-      </c>
-      <c r="D40" t="n">
-        <v>2352.02</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-2352.02</v>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>

--- a/financas_casa.xlsx
+++ b/financas_casa.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Transações" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Compras Casa" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Contas Fixas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gastos Filho" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Resumo Mensal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transações" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compras Casa" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas Fixas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gastos Filho" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo Mensal" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -124,6 +124,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -699,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1184,9 +1190,9 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>Pago</t>
         </is>
       </c>
       <c r="Q6" s="6" t="n">
@@ -2082,6 +2088,1202 @@
       </c>
       <c r="R18" s="4" t="n">
         <v>2352.02</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Jogo de copos</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Havan</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Compra a vista</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Compra_Cozinha_Jogo_de_copos_2026-03-15_22-17-10.jpeg</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Triturador de alho</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Havan</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Compra a vista</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Compra_Cozinha_Triturador_de_alho_2026-03-15_22-17-54.jpeg</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Panela de pressão eletrica</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>pagamento no cartão santander</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>51.88</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Panela de pressão eletrica</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>pagamento no cartão santander</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>51.88</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Panela de pressão eletrica</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>pagamento no cartão santander</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>51.88</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Panela de pressão eletrica</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>pagamento no cartão santander</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>51.88</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Panela de pressão eletrica</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>pagamento no cartão santander</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>51.88</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Panela de pressão eletrica</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>pagamento no cartão santander</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>51.88</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Panela de pressão eletrica</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>pagamento no cartão santander</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v>51.88</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>utensilio domesticos</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Shopping 20</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Comprado a vista</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
+      <c r="L28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>utensilio domesticos</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>mais utilidades</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Comprado a vista</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>utensilio domesticos</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Ja utilidade</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Comprado a vista</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Purificador de agua</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Mercado livre</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>541.99</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Compra a vista</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Compra_Cozinha_Purificador_de_agua_2026-03-19_13-35-55.jpeg</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v>541.99</v>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v>541.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Cama Nazare</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>📦 Outros</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Djalma moveis</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Parceiro(a)</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Compra parcelada</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Cama Nazare</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>📦 Outros</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Djalma moveis</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Parceiro(a)</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>penultima parcela</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P33" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Cama Nazare</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>📦 Outros</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Djalma moveis</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Parceiro(a)</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Ultima parcela</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +3297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2186,21 +3388,21 @@
         <v>49.9</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Eu</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Pago</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>04/2026</t>
+          <t>03/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -2210,6 +3412,53 @@
       </c>
       <c r="J2" s="5" t="inlineStr"/>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Remedio jose Eldes</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>🏥 Saúde</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Parceiro(a)</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Dia de compra do remedio do Jose Eldes</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -2226,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2245,6 +3494,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -2326,6 +3576,275 @@
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Pagamento</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Recorrente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plano de saude </t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>🏥 Saúde/Médico</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>241.36</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="4" t="n">
+        <v>241.36</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>241.36</v>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plano de saude </t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>🏥 Saúde/Médico</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>241.36</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="n">
+        <v>241.36</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>241.36</v>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plano de saude </t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>🏥 Saúde/Médico</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>286.32</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="n">
+        <v>286.32</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>286.32</v>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Bombinha de asma</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>💊 Medicamentos</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>compra mensal</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -2340,7 +3859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2525,7 +4044,16 @@
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="3" t="n"/>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="5" t="n"/>
+    </row>
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
@@ -2629,361 +4157,815 @@
     <row r="116"/>
     <row r="117"/>
     <row r="118"/>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266"/>
+    <row r="267"/>
+    <row r="268"/>
+    <row r="269"/>
+    <row r="270"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275"/>
+    <row r="276"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
+    <row r="280"/>
+    <row r="281"/>
+    <row r="282"/>
+    <row r="283"/>
+    <row r="284"/>
+    <row r="285"/>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288"/>
+    <row r="289"/>
+    <row r="290"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
+    <row r="294"/>
+    <row r="295"/>
+    <row r="296"/>
+    <row r="297"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
+    <row r="301"/>
+    <row r="302"/>
+    <row r="303"/>
+    <row r="304"/>
+    <row r="305"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
+    <row r="309"/>
+    <row r="310"/>
+    <row r="311"/>
+    <row r="312"/>
+    <row r="313"/>
+    <row r="314"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
+    <row r="318"/>
+    <row r="319"/>
+    <row r="320"/>
+    <row r="321"/>
+    <row r="322"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
+    <row r="326"/>
+    <row r="327"/>
+    <row r="328"/>
+    <row r="329"/>
+    <row r="330"/>
+    <row r="331"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
+    <row r="335"/>
+    <row r="336"/>
+    <row r="337"/>
+    <row r="338"/>
+    <row r="339"/>
+    <row r="340"/>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
+    <row r="347"/>
+    <row r="348"/>
+    <row r="349"/>
+    <row r="350"/>
+    <row r="351"/>
+    <row r="352"/>
+    <row r="353"/>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
+    <row r="358"/>
+    <row r="359"/>
+    <row r="360"/>
+    <row r="361"/>
+    <row r="362"/>
+    <row r="363"/>
+    <row r="364"/>
+    <row r="365"/>
+    <row r="366"/>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369"/>
+    <row r="370"/>
+    <row r="371"/>
+    <row r="372"/>
+    <row r="373"/>
+    <row r="374"/>
+    <row r="375"/>
+    <row r="376"/>
+    <row r="377"/>
+    <row r="378"/>
+    <row r="379"/>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382"/>
+    <row r="383"/>
+    <row r="384"/>
+    <row r="385"/>
+    <row r="386"/>
+    <row r="387"/>
+    <row r="388"/>
+    <row r="389"/>
+    <row r="390"/>
+    <row r="391"/>
+    <row r="392"/>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395"/>
+    <row r="396"/>
+    <row r="397"/>
+    <row r="398"/>
+    <row r="399"/>
+    <row r="400"/>
+    <row r="401"/>
+    <row r="402"/>
+    <row r="403"/>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408"/>
+    <row r="409"/>
+    <row r="410"/>
+    <row r="411"/>
+    <row r="412"/>
+    <row r="413"/>
+    <row r="414"/>
+    <row r="415"/>
+    <row r="416"/>
+    <row r="417"/>
+    <row r="418"/>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423"/>
+    <row r="424"/>
+    <row r="425"/>
+    <row r="426"/>
+    <row r="427"/>
+    <row r="428"/>
+    <row r="429"/>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435"/>
+    <row r="436"/>
+    <row r="437"/>
+    <row r="438"/>
+    <row r="439"/>
+    <row r="440"/>
+    <row r="441"/>
+    <row r="442"/>
+    <row r="443"/>
+    <row r="444"/>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449"/>
+    <row r="450"/>
+    <row r="451"/>
+    <row r="452"/>
+    <row r="453"/>
+    <row r="454"/>
+    <row r="455"/>
+    <row r="456"/>
+    <row r="457"/>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461"/>
+    <row r="462"/>
+    <row r="463"/>
+    <row r="464"/>
+    <row r="465"/>
+    <row r="466"/>
+    <row r="467"/>
+    <row r="468"/>
+    <row r="469"/>
+    <row r="470"/>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473"/>
+    <row r="474"/>
+    <row r="475"/>
+    <row r="476"/>
+    <row r="477"/>
+    <row r="478"/>
+    <row r="479"/>
+    <row r="480"/>
+    <row r="481"/>
+    <row r="482"/>
+    <row r="483"/>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486"/>
+    <row r="487"/>
+    <row r="488"/>
+    <row r="489"/>
+    <row r="490"/>
+    <row r="491"/>
+    <row r="492"/>
+    <row r="493"/>
+    <row r="494"/>
+    <row r="495"/>
+    <row r="496"/>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499"/>
+    <row r="500"/>
+    <row r="501"/>
+    <row r="502"/>
+    <row r="503"/>
+    <row r="504"/>
+    <row r="505"/>
+    <row r="506"/>
+    <row r="507"/>
+    <row r="508"/>
+    <row r="509"/>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512"/>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>0</v>
+      </c>
+      <c r="C513" t="n">
+        <v>286.32</v>
+      </c>
+      <c r="D513" t="n">
+        <v>0</v>
+      </c>
+      <c r="E513" t="n">
+        <v>0</v>
+      </c>
+      <c r="F513" t="n">
+        <v>286.32</v>
+      </c>
+      <c r="G513" t="n">
+        <v>-286.32</v>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>0</v>
+      </c>
+      <c r="C514" t="n">
+        <v>241.36</v>
+      </c>
+      <c r="D514" t="n">
+        <v>0</v>
+      </c>
+      <c r="E514" t="n">
+        <v>0</v>
+      </c>
+      <c r="F514" t="n">
+        <v>241.36</v>
+      </c>
+      <c r="G514" t="n">
+        <v>-241.36</v>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B119" t="n">
+      <c r="B515" t="n">
         <v>1500</v>
       </c>
-      <c r="C119" t="n">
-        <v>3139.44</v>
-      </c>
-      <c r="D119" t="n">
-        <v>3139.44</v>
-      </c>
-      <c r="E119" t="n">
+      <c r="C515" t="n">
+        <v>4651.69</v>
+      </c>
+      <c r="D515" t="n">
+        <v>4060.43</v>
+      </c>
+      <c r="E515" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="F515" t="n">
+        <v>391.36</v>
+      </c>
+      <c r="G515" t="n">
+        <v>-3151.69</v>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>700</v>
+      </c>
+      <c r="C516" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="D516" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="E516" t="n">
         <v>0</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F516" t="n">
         <v>0</v>
       </c>
-      <c r="G119" t="n">
-        <v>-1639.44</v>
-      </c>
-      <c r="H119" t="inlineStr">
+      <c r="G516" t="n">
+        <v>323.29</v>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>0</v>
+      </c>
+      <c r="C517" t="n">
+        <v>326.71</v>
+      </c>
+      <c r="D517" t="n">
+        <v>326.71</v>
+      </c>
+      <c r="E517" t="n">
+        <v>0</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0</v>
+      </c>
+      <c r="G517" t="n">
+        <v>-326.71</v>
+      </c>
+      <c r="H517" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>700</v>
-      </c>
-      <c r="C120" t="n">
-        <v>224.73</v>
-      </c>
-      <c r="D120" t="n">
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0</v>
+      </c>
+      <c r="C518" t="n">
+        <v>226.71</v>
+      </c>
+      <c r="D518" t="n">
+        <v>226.71</v>
+      </c>
+      <c r="E518" t="n">
+        <v>0</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0</v>
+      </c>
+      <c r="G518" t="n">
+        <v>-226.71</v>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0</v>
+      </c>
+      <c r="C519" t="n">
+        <v>226.71</v>
+      </c>
+      <c r="D519" t="n">
+        <v>226.71</v>
+      </c>
+      <c r="E519" t="n">
+        <v>0</v>
+      </c>
+      <c r="F519" t="n">
+        <v>0</v>
+      </c>
+      <c r="G519" t="n">
+        <v>-226.71</v>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0</v>
+      </c>
+      <c r="C520" t="n">
+        <v>226.71</v>
+      </c>
+      <c r="D520" t="n">
+        <v>226.71</v>
+      </c>
+      <c r="E520" t="n">
+        <v>0</v>
+      </c>
+      <c r="F520" t="n">
+        <v>0</v>
+      </c>
+      <c r="G520" t="n">
+        <v>-226.71</v>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>0</v>
+      </c>
+      <c r="C521" t="n">
+        <v>226.71</v>
+      </c>
+      <c r="D521" t="n">
+        <v>226.71</v>
+      </c>
+      <c r="E521" t="n">
+        <v>0</v>
+      </c>
+      <c r="F521" t="n">
+        <v>0</v>
+      </c>
+      <c r="G521" t="n">
+        <v>-226.71</v>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>0</v>
+      </c>
+      <c r="C522" t="n">
+        <v>226.71</v>
+      </c>
+      <c r="D522" t="n">
+        <v>226.71</v>
+      </c>
+      <c r="E522" t="n">
+        <v>0</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0</v>
+      </c>
+      <c r="G522" t="n">
+        <v>-226.71</v>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>0</v>
+      </c>
+      <c r="C523" t="n">
         <v>174.83</v>
       </c>
-      <c r="E120" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="F120" t="n">
+      <c r="D523" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E523" t="n">
         <v>0</v>
       </c>
-      <c r="G120" t="n">
-        <v>475.27</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
+      <c r="F523" t="n">
         <v>0</v>
       </c>
-      <c r="C121" t="n">
+      <c r="G523" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>0</v>
+      </c>
+      <c r="C524" t="n">
         <v>174.83</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D524" t="n">
         <v>174.83</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E524" t="n">
         <v>0</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F524" t="n">
         <v>0</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G524" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H524" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
         <v>0</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C525" t="n">
         <v>174.83</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D525" t="n">
         <v>174.83</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E525" t="n">
         <v>0</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F525" t="n">
         <v>0</v>
       </c>
-      <c r="G122" t="n">
+      <c r="G525" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H525" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
         <v>0</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C526" t="n">
         <v>174.83</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D526" t="n">
         <v>174.83</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E526" t="n">
         <v>0</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F526" t="n">
         <v>0</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G526" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D124" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D125" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D126" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
-      <c r="C127" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D127" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E127" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D128" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D129" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D130" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H130" t="inlineStr">
+      <c r="H526" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>

--- a/financas_casa.xlsx
+++ b/financas_casa.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transações" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compras Casa" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas Fixas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gastos Filho" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo Mensal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Transações" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Compras Casa" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Contas Fixas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gastos Filho" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Resumo Mensal" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -694,6 +694,186 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>drenagem linfática</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>🏥 Saúde</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Parceiro(a)</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Transacao_Saude_drenagem_linfatica_2026-03-23_19-14-09.pdf</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Compra pra casa</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>🍔 Alimentação</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Compras da casa</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Transacao_Alimentacao_Compra_pra_casa_2026-03-31_20-58-19.jpeg</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Compra pra casa</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>🍔 Alimentação</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>418.35</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Compras da casa no sams club</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>mercado para casa</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>🍔 Alimentação</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>pago a vista</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -705,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2987,303 +3167,1237 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Purificador de agua</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="A31" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Cama Nazare</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>📦 Outros</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Djalma moveis</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Parceiro(a)</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Compra parcelada</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Cama Nazare</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>📦 Outros</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Djalma moveis</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Parceiro(a)</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>penultima parcela</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Cama Nazare</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>📦 Outros</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Djalma moveis</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Parceiro(a)</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Ultima parcela</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>putificador de agua everest</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Compra_Eletrodomesticos_putificador_de_agua_everest_2026-03-27_12-08-56.jpeg</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v>133.63</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>putificador de agua everest</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="R35" s="4" t="n">
+        <v>133.63</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>putificador de agua everest</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v>133.63</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>putificador de agua everest</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="R37" s="4" t="n">
+        <v>133.63</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>putificador de agua everest</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v>133.63</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>putificador de agua everest</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="inlineStr"/>
+      <c r="L39" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="R39" s="4" t="n">
+        <v>133.63</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>putificador de agua everest</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M40" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N40" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v>133.63</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>putificador de agua everest</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="R41" s="4" t="n">
+        <v>133.63</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>putificador de agua everest</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr"/>
+      <c r="L42" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="N42" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>2026-11-23</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v>133.63</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>putificador de agua everest</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Parcelado</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-23</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>1336.34</v>
+      </c>
+      <c r="R43" s="4" t="n">
+        <v>133.63</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>pote de plarico</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>🍳 Cozinha</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Mercado livre</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Ferreira costa</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Eu</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>compra a vista</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>Compra_Cozinha_pote_de_plarico_2026-03-31_20-53-26.jpeg</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Ventilador</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>🏠 Eletrodomésticos</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Ambos</t>
         </is>
       </c>
-      <c r="G31" s="6" t="n">
-        <v>541.99</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="G45" s="6" t="n">
+        <v>170.83</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Comprado</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Compra a vista</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Compra_Cozinha_Purificador_de_agua_2026-03-19_13-35-55.jpeg</t>
-        </is>
-      </c>
-      <c r="L31" s="5" t="n">
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>Compra_Eletrodomesticos_Ventilador_2026-04-03_10-18-22.jpeg</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M31" s="5" t="n">
+      <c r="M45" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="5" t="n">
+      <c r="N45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v>170.83</v>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v>170.83</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Coisas para construção</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>🔧 Ferramentas/Manutenção</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Carajas</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Parceiro(a)</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>222.36</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>caixas de luz, impermeabilizante, assento para vaso</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Compra_Ferramentas_Manutencao_Coisas_para_construcao_2026-04-06_20-21-33.jpeg</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="inlineStr">
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
         <is>
           <t>Pago</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v>541.99</v>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v>541.99</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Cama Nazare</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>📦 Outros</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Djalma moveis</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Parceiro(a)</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="Q46" s="4" t="n">
+        <v>222.36</v>
+      </c>
+      <c r="R46" s="4" t="n">
+        <v>222.36</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Compras para casa</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>🍳 Cozinha</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Freitas</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>334.95</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Comprado</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>Compra parcelada</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="n">
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Cadeiras, potes de vidro e grill</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M47" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="R32" s="4" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Cama Nazare</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>📦 Outros</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Djalma moveis</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Parceiro(a)</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>penultima parcela</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v>150</v>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Cama Nazare</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>📦 Outros</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Djalma moveis</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Parceiro(a)</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>Média</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>Ultima parcela</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="R34" s="4" t="n">
-        <v>100</v>
+      <c r="N47" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v>334.95</v>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v>334.95</v>
       </c>
     </row>
   </sheetData>
@@ -3475,7 +4589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3806,7 +4920,11 @@
       <c r="F5" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Filho_Medicamentos_Bombinha_de_asma_2026-04-03_10-09-19.jpeg</t>
+        </is>
+      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>compra mensal</t>
@@ -3820,7 +4938,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="L5" s="5" t="n">
@@ -3837,14 +4955,87 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="P5" s="9" t="inlineStr">
+        <is>
+          <t>Pago</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Sabonete</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>🧴 Higiene/Fraldas</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Filho_Higiene_Fraldas_Sabonete_2026-04-06_20-52-21.jpeg</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Sabonete anti alergico</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
         </is>
       </c>
     </row>
@@ -3859,7 +5050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H526"/>
+  <dimension ref="A1:H778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4551,421 +5742,673 @@
     <row r="510"/>
     <row r="511"/>
     <row r="512"/>
-    <row r="513">
-      <c r="A513" t="inlineStr">
+    <row r="513"/>
+    <row r="514"/>
+    <row r="515"/>
+    <row r="516"/>
+    <row r="517"/>
+    <row r="518"/>
+    <row r="519"/>
+    <row r="520"/>
+    <row r="521"/>
+    <row r="522"/>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
+    <row r="526"/>
+    <row r="527"/>
+    <row r="528"/>
+    <row r="529"/>
+    <row r="530"/>
+    <row r="531"/>
+    <row r="532"/>
+    <row r="533"/>
+    <row r="534"/>
+    <row r="535"/>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538"/>
+    <row r="539"/>
+    <row r="540"/>
+    <row r="541"/>
+    <row r="542"/>
+    <row r="543"/>
+    <row r="544"/>
+    <row r="545"/>
+    <row r="546"/>
+    <row r="547"/>
+    <row r="548"/>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
+    <row r="552"/>
+    <row r="553"/>
+    <row r="554"/>
+    <row r="555"/>
+    <row r="556"/>
+    <row r="557"/>
+    <row r="558"/>
+    <row r="559"/>
+    <row r="560"/>
+    <row r="561"/>
+    <row r="562"/>
+    <row r="563"/>
+    <row r="564"/>
+    <row r="565"/>
+    <row r="566"/>
+    <row r="567"/>
+    <row r="568"/>
+    <row r="569"/>
+    <row r="570"/>
+    <row r="571"/>
+    <row r="572"/>
+    <row r="573"/>
+    <row r="574"/>
+    <row r="575"/>
+    <row r="576"/>
+    <row r="577"/>
+    <row r="578"/>
+    <row r="579"/>
+    <row r="580"/>
+    <row r="581"/>
+    <row r="582"/>
+    <row r="583"/>
+    <row r="584"/>
+    <row r="585"/>
+    <row r="586"/>
+    <row r="587"/>
+    <row r="588"/>
+    <row r="589"/>
+    <row r="590"/>
+    <row r="591"/>
+    <row r="592"/>
+    <row r="593"/>
+    <row r="594"/>
+    <row r="595"/>
+    <row r="596"/>
+    <row r="597"/>
+    <row r="598"/>
+    <row r="599"/>
+    <row r="600"/>
+    <row r="601"/>
+    <row r="602"/>
+    <row r="603"/>
+    <row r="604"/>
+    <row r="605"/>
+    <row r="606"/>
+    <row r="607"/>
+    <row r="608"/>
+    <row r="609"/>
+    <row r="610"/>
+    <row r="611"/>
+    <row r="612"/>
+    <row r="613"/>
+    <row r="614"/>
+    <row r="615"/>
+    <row r="616"/>
+    <row r="617"/>
+    <row r="618"/>
+    <row r="619"/>
+    <row r="620"/>
+    <row r="621"/>
+    <row r="622"/>
+    <row r="623"/>
+    <row r="624"/>
+    <row r="625"/>
+    <row r="626"/>
+    <row r="627"/>
+    <row r="628"/>
+    <row r="629"/>
+    <row r="630"/>
+    <row r="631"/>
+    <row r="632"/>
+    <row r="633"/>
+    <row r="634"/>
+    <row r="635"/>
+    <row r="636"/>
+    <row r="637"/>
+    <row r="638"/>
+    <row r="639"/>
+    <row r="640"/>
+    <row r="641"/>
+    <row r="642"/>
+    <row r="643"/>
+    <row r="644"/>
+    <row r="645"/>
+    <row r="646"/>
+    <row r="647"/>
+    <row r="648"/>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
+    <row r="700"/>
+    <row r="701"/>
+    <row r="702"/>
+    <row r="703"/>
+    <row r="704"/>
+    <row r="705"/>
+    <row r="706"/>
+    <row r="707"/>
+    <row r="708"/>
+    <row r="709"/>
+    <row r="710"/>
+    <row r="711"/>
+    <row r="712"/>
+    <row r="713"/>
+    <row r="714"/>
+    <row r="715"/>
+    <row r="716"/>
+    <row r="717"/>
+    <row r="718"/>
+    <row r="719"/>
+    <row r="720"/>
+    <row r="721"/>
+    <row r="722"/>
+    <row r="723"/>
+    <row r="724"/>
+    <row r="725"/>
+    <row r="726"/>
+    <row r="727"/>
+    <row r="728"/>
+    <row r="729"/>
+    <row r="730"/>
+    <row r="731"/>
+    <row r="732"/>
+    <row r="733"/>
+    <row r="734"/>
+    <row r="735"/>
+    <row r="736"/>
+    <row r="737"/>
+    <row r="738"/>
+    <row r="739"/>
+    <row r="740"/>
+    <row r="741"/>
+    <row r="742"/>
+    <row r="743"/>
+    <row r="744"/>
+    <row r="745"/>
+    <row r="746"/>
+    <row r="747"/>
+    <row r="748"/>
+    <row r="749"/>
+    <row r="750"/>
+    <row r="751"/>
+    <row r="752"/>
+    <row r="753"/>
+    <row r="754"/>
+    <row r="755"/>
+    <row r="756"/>
+    <row r="757"/>
+    <row r="758"/>
+    <row r="759"/>
+    <row r="760"/>
+    <row r="761"/>
+    <row r="762"/>
+    <row r="763"/>
+    <row r="764"/>
+    <row r="765">
+      <c r="A765" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B513" t="n">
+      <c r="B765" t="n">
         <v>0</v>
       </c>
-      <c r="C513" t="n">
+      <c r="C765" t="n">
         <v>286.32</v>
       </c>
-      <c r="D513" t="n">
+      <c r="D765" t="n">
         <v>0</v>
       </c>
-      <c r="E513" t="n">
+      <c r="E765" t="n">
         <v>0</v>
       </c>
-      <c r="F513" t="n">
+      <c r="F765" t="n">
         <v>286.32</v>
       </c>
-      <c r="G513" t="n">
+      <c r="G765" t="n">
         <v>-286.32</v>
       </c>
-      <c r="H513" t="inlineStr">
+      <c r="H765" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
+    <row r="766">
+      <c r="A766" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B514" t="n">
+      <c r="B766" t="n">
         <v>0</v>
       </c>
-      <c r="C514" t="n">
+      <c r="C766" t="n">
         <v>241.36</v>
       </c>
-      <c r="D514" t="n">
+      <c r="D766" t="n">
         <v>0</v>
       </c>
-      <c r="E514" t="n">
+      <c r="E766" t="n">
         <v>0</v>
       </c>
-      <c r="F514" t="n">
+      <c r="F766" t="n">
         <v>241.36</v>
       </c>
-      <c r="G514" t="n">
+      <c r="G766" t="n">
         <v>-241.36</v>
       </c>
-      <c r="H514" t="inlineStr">
+      <c r="H766" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
+    <row r="767">
+      <c r="A767" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B515" t="n">
+      <c r="B767" t="n">
         <v>1500</v>
       </c>
-      <c r="C515" t="n">
-        <v>4651.69</v>
-      </c>
-      <c r="D515" t="n">
-        <v>4060.43</v>
-      </c>
-      <c r="E515" t="n">
+      <c r="C767" t="n">
+        <v>5011.28</v>
+      </c>
+      <c r="D767" t="n">
+        <v>3671.87</v>
+      </c>
+      <c r="E767" t="n">
         <v>199.9</v>
       </c>
-      <c r="F515" t="n">
+      <c r="F767" t="n">
         <v>391.36</v>
       </c>
-      <c r="G515" t="n">
-        <v>-3151.69</v>
-      </c>
-      <c r="H515" t="inlineStr">
+      <c r="G767" t="n">
+        <v>-3511.28</v>
+      </c>
+      <c r="H767" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
+    <row r="768">
+      <c r="A768" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B516" t="n">
+      <c r="B768" t="n">
         <v>700</v>
       </c>
-      <c r="C516" t="n">
-        <v>376.71</v>
-      </c>
-      <c r="D516" t="n">
-        <v>376.71</v>
-      </c>
-      <c r="E516" t="n">
+      <c r="C768" t="n">
+        <v>1552.47</v>
+      </c>
+      <c r="D768" t="n">
+        <v>1238.48</v>
+      </c>
+      <c r="E768" t="n">
         <v>0</v>
       </c>
-      <c r="F516" t="n">
+      <c r="F768" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="G768" t="n">
+        <v>-852.47</v>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
         <v>0</v>
       </c>
-      <c r="G516" t="n">
-        <v>323.29</v>
-      </c>
-      <c r="H516" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B517" t="n">
+      <c r="C769" t="n">
+        <v>460.34</v>
+      </c>
+      <c r="D769" t="n">
+        <v>460.34</v>
+      </c>
+      <c r="E769" t="n">
         <v>0</v>
       </c>
-      <c r="C517" t="n">
-        <v>326.71</v>
-      </c>
-      <c r="D517" t="n">
-        <v>326.71</v>
-      </c>
-      <c r="E517" t="n">
+      <c r="F769" t="n">
         <v>0</v>
       </c>
-      <c r="F517" t="n">
+      <c r="G769" t="n">
+        <v>-460.34</v>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
         <v>0</v>
       </c>
-      <c r="G517" t="n">
-        <v>-326.71</v>
-      </c>
-      <c r="H517" t="inlineStr">
+      <c r="C770" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="D770" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="E770" t="n">
+        <v>0</v>
+      </c>
+      <c r="F770" t="n">
+        <v>0</v>
+      </c>
+      <c r="G770" t="n">
+        <v>-360.34</v>
+      </c>
+      <c r="H770" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B518" t="n">
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
         <v>0</v>
       </c>
-      <c r="C518" t="n">
-        <v>226.71</v>
-      </c>
-      <c r="D518" t="n">
-        <v>226.71</v>
-      </c>
-      <c r="E518" t="n">
+      <c r="C771" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="D771" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="E771" t="n">
         <v>0</v>
       </c>
-      <c r="F518" t="n">
+      <c r="F771" t="n">
         <v>0</v>
       </c>
-      <c r="G518" t="n">
-        <v>-226.71</v>
-      </c>
-      <c r="H518" t="inlineStr">
+      <c r="G771" t="n">
+        <v>-360.34</v>
+      </c>
+      <c r="H771" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B519" t="n">
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
         <v>0</v>
       </c>
-      <c r="C519" t="n">
-        <v>226.71</v>
-      </c>
-      <c r="D519" t="n">
-        <v>226.71</v>
-      </c>
-      <c r="E519" t="n">
+      <c r="C772" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="D772" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="E772" t="n">
         <v>0</v>
       </c>
-      <c r="F519" t="n">
+      <c r="F772" t="n">
         <v>0</v>
       </c>
-      <c r="G519" t="n">
-        <v>-226.71</v>
-      </c>
-      <c r="H519" t="inlineStr">
+      <c r="G772" t="n">
+        <v>-360.34</v>
+      </c>
+      <c r="H772" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B520" t="n">
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
         <v>0</v>
       </c>
-      <c r="C520" t="n">
-        <v>226.71</v>
-      </c>
-      <c r="D520" t="n">
-        <v>226.71</v>
-      </c>
-      <c r="E520" t="n">
+      <c r="C773" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="D773" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="E773" t="n">
         <v>0</v>
       </c>
-      <c r="F520" t="n">
+      <c r="F773" t="n">
         <v>0</v>
       </c>
-      <c r="G520" t="n">
-        <v>-226.71</v>
-      </c>
-      <c r="H520" t="inlineStr">
+      <c r="G773" t="n">
+        <v>-360.34</v>
+      </c>
+      <c r="H773" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B521" t="n">
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B774" t="n">
         <v>0</v>
       </c>
-      <c r="C521" t="n">
-        <v>226.71</v>
-      </c>
-      <c r="D521" t="n">
-        <v>226.71</v>
-      </c>
-      <c r="E521" t="n">
+      <c r="C774" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="D774" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="E774" t="n">
         <v>0</v>
       </c>
-      <c r="F521" t="n">
+      <c r="F774" t="n">
         <v>0</v>
       </c>
-      <c r="G521" t="n">
-        <v>-226.71</v>
-      </c>
-      <c r="H521" t="inlineStr">
+      <c r="G774" t="n">
+        <v>-360.34</v>
+      </c>
+      <c r="H774" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B522" t="n">
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B775" t="n">
         <v>0</v>
       </c>
-      <c r="C522" t="n">
-        <v>226.71</v>
-      </c>
-      <c r="D522" t="n">
-        <v>226.71</v>
-      </c>
-      <c r="E522" t="n">
+      <c r="C775" t="n">
+        <v>308.46</v>
+      </c>
+      <c r="D775" t="n">
+        <v>308.46</v>
+      </c>
+      <c r="E775" t="n">
         <v>0</v>
       </c>
-      <c r="F522" t="n">
+      <c r="F775" t="n">
         <v>0</v>
       </c>
-      <c r="G522" t="n">
-        <v>-226.71</v>
-      </c>
-      <c r="H522" t="inlineStr">
+      <c r="G775" t="n">
+        <v>-308.46</v>
+      </c>
+      <c r="H775" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="B523" t="n">
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B776" t="n">
         <v>0</v>
       </c>
-      <c r="C523" t="n">
+      <c r="C776" t="n">
+        <v>308.46</v>
+      </c>
+      <c r="D776" t="n">
+        <v>308.46</v>
+      </c>
+      <c r="E776" t="n">
+        <v>0</v>
+      </c>
+      <c r="F776" t="n">
+        <v>0</v>
+      </c>
+      <c r="G776" t="n">
+        <v>-308.46</v>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="B777" t="n">
+        <v>0</v>
+      </c>
+      <c r="C777" t="n">
         <v>174.83</v>
       </c>
-      <c r="D523" t="n">
+      <c r="D777" t="n">
         <v>174.83</v>
       </c>
-      <c r="E523" t="n">
+      <c r="E777" t="n">
         <v>0</v>
       </c>
-      <c r="F523" t="n">
+      <c r="F777" t="n">
         <v>0</v>
       </c>
-      <c r="G523" t="n">
+      <c r="G777" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H523" t="inlineStr">
+      <c r="H777" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B524" t="n">
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="B778" t="n">
         <v>0</v>
       </c>
-      <c r="C524" t="n">
+      <c r="C778" t="n">
         <v>174.83</v>
       </c>
-      <c r="D524" t="n">
+      <c r="D778" t="n">
         <v>174.83</v>
       </c>
-      <c r="E524" t="n">
+      <c r="E778" t="n">
         <v>0</v>
       </c>
-      <c r="F524" t="n">
+      <c r="F778" t="n">
         <v>0</v>
       </c>
-      <c r="G524" t="n">
+      <c r="G778" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H524" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="B525" t="n">
-        <v>0</v>
-      </c>
-      <c r="C525" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D525" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E525" t="n">
-        <v>0</v>
-      </c>
-      <c r="F525" t="n">
-        <v>0</v>
-      </c>
-      <c r="G525" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H525" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="B526" t="n">
-        <v>0</v>
-      </c>
-      <c r="C526" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D526" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E526" t="n">
-        <v>0</v>
-      </c>
-      <c r="F526" t="n">
-        <v>0</v>
-      </c>
-      <c r="G526" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H526" t="inlineStr">
+      <c r="H778" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>

--- a/financas_casa.xlsx
+++ b/financas_casa.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -869,6 +869,54 @@
       </c>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>compras para a casa</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>🔧 Manutenção</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>93.42</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>lava roupa e outros materiais de cozinha</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Transacao_Manutencao_compras_para_a_casa_2026-04-09_17-19-37.jpeg</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
@@ -4725,13 +4773,17 @@
       <c r="F2" s="4" t="n">
         <v>241.36</v>
       </c>
-      <c r="G2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Filho_Saude_Medico_Plano_de_saude_2026-04-09_15-34-24.jpeg</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="4" t="n">
-        <v>241.36</v>
+        <v>250.38</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>241.36</v>
+        <v>250.38</v>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
@@ -4752,9 +4804,9 @@
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="P2" s="10" t="inlineStr">
+        <is>
+          <t>Pago</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -5050,7 +5102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H778"/>
+  <dimension ref="A1:H820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5994,421 +6046,463 @@
     <row r="762"/>
     <row r="763"/>
     <row r="764"/>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="765"/>
+    <row r="766"/>
+    <row r="767"/>
+    <row r="768"/>
+    <row r="769"/>
+    <row r="770"/>
+    <row r="771"/>
+    <row r="772"/>
+    <row r="773"/>
+    <row r="774"/>
+    <row r="775"/>
+    <row r="776"/>
+    <row r="777"/>
+    <row r="778"/>
+    <row r="779"/>
+    <row r="780"/>
+    <row r="781"/>
+    <row r="782"/>
+    <row r="783"/>
+    <row r="784"/>
+    <row r="785"/>
+    <row r="786"/>
+    <row r="787"/>
+    <row r="788"/>
+    <row r="789"/>
+    <row r="790"/>
+    <row r="791"/>
+    <row r="792"/>
+    <row r="793"/>
+    <row r="794"/>
+    <row r="795"/>
+    <row r="796"/>
+    <row r="797"/>
+    <row r="798"/>
+    <row r="799"/>
+    <row r="800"/>
+    <row r="801"/>
+    <row r="802"/>
+    <row r="803"/>
+    <row r="804"/>
+    <row r="805"/>
+    <row r="806"/>
+    <row r="807">
+      <c r="A807" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B765" t="n">
+      <c r="B807" t="n">
         <v>0</v>
       </c>
-      <c r="C765" t="n">
+      <c r="C807" t="n">
         <v>286.32</v>
       </c>
-      <c r="D765" t="n">
+      <c r="D807" t="n">
         <v>0</v>
       </c>
-      <c r="E765" t="n">
+      <c r="E807" t="n">
         <v>0</v>
       </c>
-      <c r="F765" t="n">
+      <c r="F807" t="n">
         <v>286.32</v>
       </c>
-      <c r="G765" t="n">
+      <c r="G807" t="n">
         <v>-286.32</v>
       </c>
-      <c r="H765" t="inlineStr">
+      <c r="H807" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="808">
+      <c r="A808" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B766" t="n">
+      <c r="B808" t="n">
         <v>0</v>
       </c>
-      <c r="C766" t="n">
+      <c r="C808" t="n">
         <v>241.36</v>
       </c>
-      <c r="D766" t="n">
+      <c r="D808" t="n">
         <v>0</v>
       </c>
-      <c r="E766" t="n">
+      <c r="E808" t="n">
         <v>0</v>
       </c>
-      <c r="F766" t="n">
+      <c r="F808" t="n">
         <v>241.36</v>
       </c>
-      <c r="G766" t="n">
+      <c r="G808" t="n">
         <v>-241.36</v>
       </c>
-      <c r="H766" t="inlineStr">
+      <c r="H808" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="809">
+      <c r="A809" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B767" t="n">
+      <c r="B809" t="n">
         <v>1500</v>
       </c>
-      <c r="C767" t="n">
-        <v>5011.28</v>
-      </c>
-      <c r="D767" t="n">
+      <c r="C809" t="n">
+        <v>5020.3</v>
+      </c>
+      <c r="D809" t="n">
         <v>3671.87</v>
       </c>
-      <c r="E767" t="n">
+      <c r="E809" t="n">
         <v>199.9</v>
       </c>
-      <c r="F767" t="n">
-        <v>391.36</v>
-      </c>
-      <c r="G767" t="n">
-        <v>-3511.28</v>
-      </c>
-      <c r="H767" t="inlineStr">
+      <c r="F809" t="n">
+        <v>400.38</v>
+      </c>
+      <c r="G809" t="n">
+        <v>-3520.3</v>
+      </c>
+      <c r="H809" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="810">
+      <c r="A810" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B768" t="n">
+      <c r="B810" t="n">
         <v>700</v>
       </c>
-      <c r="C768" t="n">
-        <v>1552.47</v>
-      </c>
-      <c r="D768" t="n">
+      <c r="C810" t="n">
+        <v>1645.89</v>
+      </c>
+      <c r="D810" t="n">
         <v>1238.48</v>
       </c>
-      <c r="E768" t="n">
+      <c r="E810" t="n">
         <v>0</v>
       </c>
-      <c r="F768" t="n">
+      <c r="F810" t="n">
         <v>33.99</v>
       </c>
-      <c r="G768" t="n">
-        <v>-852.47</v>
-      </c>
-      <c r="H768" t="inlineStr">
+      <c r="G810" t="n">
+        <v>-945.8900000000001</v>
+      </c>
+      <c r="H810" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="811">
+      <c r="A811" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B769" t="n">
+      <c r="B811" t="n">
         <v>0</v>
       </c>
-      <c r="C769" t="n">
+      <c r="C811" t="n">
         <v>460.34</v>
       </c>
-      <c r="D769" t="n">
+      <c r="D811" t="n">
         <v>460.34</v>
       </c>
-      <c r="E769" t="n">
+      <c r="E811" t="n">
         <v>0</v>
       </c>
-      <c r="F769" t="n">
+      <c r="F811" t="n">
         <v>0</v>
       </c>
-      <c r="G769" t="n">
+      <c r="G811" t="n">
         <v>-460.34</v>
       </c>
-      <c r="H769" t="inlineStr">
+      <c r="H811" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="812">
+      <c r="A812" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B770" t="n">
+      <c r="B812" t="n">
         <v>0</v>
       </c>
-      <c r="C770" t="n">
+      <c r="C812" t="n">
         <v>360.34</v>
       </c>
-      <c r="D770" t="n">
+      <c r="D812" t="n">
         <v>360.34</v>
       </c>
-      <c r="E770" t="n">
+      <c r="E812" t="n">
         <v>0</v>
       </c>
-      <c r="F770" t="n">
+      <c r="F812" t="n">
         <v>0</v>
       </c>
-      <c r="G770" t="n">
+      <c r="G812" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H770" t="inlineStr">
+      <c r="H812" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="813">
+      <c r="A813" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B771" t="n">
+      <c r="B813" t="n">
         <v>0</v>
       </c>
-      <c r="C771" t="n">
+      <c r="C813" t="n">
         <v>360.34</v>
       </c>
-      <c r="D771" t="n">
+      <c r="D813" t="n">
         <v>360.34</v>
       </c>
-      <c r="E771" t="n">
+      <c r="E813" t="n">
         <v>0</v>
       </c>
-      <c r="F771" t="n">
+      <c r="F813" t="n">
         <v>0</v>
       </c>
-      <c r="G771" t="n">
+      <c r="G813" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H771" t="inlineStr">
+      <c r="H813" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="814">
+      <c r="A814" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B772" t="n">
+      <c r="B814" t="n">
         <v>0</v>
       </c>
-      <c r="C772" t="n">
+      <c r="C814" t="n">
         <v>360.34</v>
       </c>
-      <c r="D772" t="n">
+      <c r="D814" t="n">
         <v>360.34</v>
       </c>
-      <c r="E772" t="n">
+      <c r="E814" t="n">
         <v>0</v>
       </c>
-      <c r="F772" t="n">
+      <c r="F814" t="n">
         <v>0</v>
       </c>
-      <c r="G772" t="n">
+      <c r="G814" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H772" t="inlineStr">
+      <c r="H814" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="815">
+      <c r="A815" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B773" t="n">
+      <c r="B815" t="n">
         <v>0</v>
       </c>
-      <c r="C773" t="n">
+      <c r="C815" t="n">
         <v>360.34</v>
       </c>
-      <c r="D773" t="n">
+      <c r="D815" t="n">
         <v>360.34</v>
       </c>
-      <c r="E773" t="n">
+      <c r="E815" t="n">
         <v>0</v>
       </c>
-      <c r="F773" t="n">
+      <c r="F815" t="n">
         <v>0</v>
       </c>
-      <c r="G773" t="n">
+      <c r="G815" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H773" t="inlineStr">
+      <c r="H815" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="816">
+      <c r="A816" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B774" t="n">
+      <c r="B816" t="n">
         <v>0</v>
       </c>
-      <c r="C774" t="n">
+      <c r="C816" t="n">
         <v>360.34</v>
       </c>
-      <c r="D774" t="n">
+      <c r="D816" t="n">
         <v>360.34</v>
       </c>
-      <c r="E774" t="n">
+      <c r="E816" t="n">
         <v>0</v>
       </c>
-      <c r="F774" t="n">
+      <c r="F816" t="n">
         <v>0</v>
       </c>
-      <c r="G774" t="n">
+      <c r="G816" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H774" t="inlineStr">
+      <c r="H816" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="817">
+      <c r="A817" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B775" t="n">
+      <c r="B817" t="n">
         <v>0</v>
       </c>
-      <c r="C775" t="n">
+      <c r="C817" t="n">
         <v>308.46</v>
       </c>
-      <c r="D775" t="n">
+      <c r="D817" t="n">
         <v>308.46</v>
       </c>
-      <c r="E775" t="n">
+      <c r="E817" t="n">
         <v>0</v>
       </c>
-      <c r="F775" t="n">
+      <c r="F817" t="n">
         <v>0</v>
       </c>
-      <c r="G775" t="n">
+      <c r="G817" t="n">
         <v>-308.46</v>
       </c>
-      <c r="H775" t="inlineStr">
+      <c r="H817" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="818">
+      <c r="A818" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B776" t="n">
+      <c r="B818" t="n">
         <v>0</v>
       </c>
-      <c r="C776" t="n">
+      <c r="C818" t="n">
         <v>308.46</v>
       </c>
-      <c r="D776" t="n">
+      <c r="D818" t="n">
         <v>308.46</v>
       </c>
-      <c r="E776" t="n">
+      <c r="E818" t="n">
         <v>0</v>
       </c>
-      <c r="F776" t="n">
+      <c r="F818" t="n">
         <v>0</v>
       </c>
-      <c r="G776" t="n">
+      <c r="G818" t="n">
         <v>-308.46</v>
       </c>
-      <c r="H776" t="inlineStr">
+      <c r="H818" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="819">
+      <c r="A819" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="B777" t="n">
+      <c r="B819" t="n">
         <v>0</v>
       </c>
-      <c r="C777" t="n">
+      <c r="C819" t="n">
         <v>174.83</v>
       </c>
-      <c r="D777" t="n">
+      <c r="D819" t="n">
         <v>174.83</v>
       </c>
-      <c r="E777" t="n">
+      <c r="E819" t="n">
         <v>0</v>
       </c>
-      <c r="F777" t="n">
+      <c r="F819" t="n">
         <v>0</v>
       </c>
-      <c r="G777" t="n">
+      <c r="G819" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H777" t="inlineStr">
+      <c r="H819" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="820">
+      <c r="A820" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="B778" t="n">
+      <c r="B820" t="n">
         <v>0</v>
       </c>
-      <c r="C778" t="n">
+      <c r="C820" t="n">
         <v>174.83</v>
       </c>
-      <c r="D778" t="n">
+      <c r="D820" t="n">
         <v>174.83</v>
       </c>
-      <c r="E778" t="n">
+      <c r="E820" t="n">
         <v>0</v>
       </c>
-      <c r="F778" t="n">
+      <c r="F820" t="n">
         <v>0</v>
       </c>
-      <c r="G778" t="n">
+      <c r="G820" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H778" t="inlineStr">
+      <c r="H820" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>

--- a/financas_casa.xlsx
+++ b/financas_casa.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -917,6 +917,194 @@
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>mussarela</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>🍔 Alimentação</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>mussarela brasil atacarejo</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Transacao_Alimentacao_mussarela_2026-04-10_21-32-36.jpeg</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Carne musculo para kibe</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>🍔 Alimentação</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Transacao_Alimentacao_Carne_musculo_para_kibe_2026-04-13_18-09-26.jpeg</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>farmacia</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>💊 Medicamentos</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Parceiro(a)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>abs intimo e lenço umidecidas</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Transacao_Medicamentos_farmacia_2026-04-13_18-31-14.jpeg</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>mercado para casa</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>🍔 Alimentação</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>pagamento a vista no dinheiro</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Transacao_Alimentacao_mercado_para_casa_2026-04-13_18-35-13.jpeg</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
@@ -4459,7 +4647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4594,7 +4782,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>150</v>
+        <v>116.65</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>23</v>
@@ -4604,23 +4792,74 @@
           <t>Parceiro(a)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>03/2026</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Dia de compra do remedio do Jose Eldes</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Conta_Saude_Remedio_jose_Eldes_2026-04-10_21-38-57.jpeg</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Pravaler</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>🎓 Educação</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>428.06</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>03/2026</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>Dia de compra do remedio do Jose Eldes</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>04/2026</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Pagamento prsvaler</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -4637,7 +4876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4951,7 +5190,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -5086,6 +5325,436 @@
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Frutas para henry</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>🍼 Alimentação/Fórmula</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Compra de frutas pago a vista</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>💊 Medicamentos</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Filho_Medicamentos_Medicamentos_2026-04-13_18-18-53.jpeg</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Compra de medicamentos, pois o henry estava doente</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Medicamentos</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>💊 Medicamentos</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>145.96</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Compra de medicamentos, pois o henry estava doente</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>145.96</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>145.96</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Medicamentos</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>💊 Medicamentos</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>145.96</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Filho_Medicamentos_Medicamentos_2026-04-13_18-23-19.jpeg</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Compra de medicamentos, pois o henry estava doente</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>145.96</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>145.96</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Frutas para henry</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>🍼 Alimentação/Fórmula</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Filho_Alimentacao_Formula_Frutas_para_henry_2026-04-13_18-26-21.jpeg</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Compra de frutas pago a vista</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Frutas para henry</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>🍼 Alimentação/Fórmula</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Filho_Alimentacao_Formula_Frutas_para_henry_2026-04-13_18-26-22.jpeg</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Compra de frutas pago a vista</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>86.38</v>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Pago</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
@@ -5102,7 +5771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H820"/>
+  <dimension ref="A1:H1128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6088,421 +6757,729 @@
     <row r="804"/>
     <row r="805"/>
     <row r="806"/>
-    <row r="807">
-      <c r="A807" t="inlineStr">
+    <row r="807"/>
+    <row r="808"/>
+    <row r="809"/>
+    <row r="810"/>
+    <row r="811"/>
+    <row r="812"/>
+    <row r="813"/>
+    <row r="814"/>
+    <row r="815"/>
+    <row r="816"/>
+    <row r="817"/>
+    <row r="818"/>
+    <row r="819"/>
+    <row r="820"/>
+    <row r="821"/>
+    <row r="822"/>
+    <row r="823"/>
+    <row r="824"/>
+    <row r="825"/>
+    <row r="826"/>
+    <row r="827"/>
+    <row r="828"/>
+    <row r="829"/>
+    <row r="830"/>
+    <row r="831"/>
+    <row r="832"/>
+    <row r="833"/>
+    <row r="834"/>
+    <row r="835"/>
+    <row r="836"/>
+    <row r="837"/>
+    <row r="838"/>
+    <row r="839"/>
+    <row r="840"/>
+    <row r="841"/>
+    <row r="842"/>
+    <row r="843"/>
+    <row r="844"/>
+    <row r="845"/>
+    <row r="846"/>
+    <row r="847"/>
+    <row r="848"/>
+    <row r="849"/>
+    <row r="850"/>
+    <row r="851"/>
+    <row r="852"/>
+    <row r="853"/>
+    <row r="854"/>
+    <row r="855"/>
+    <row r="856"/>
+    <row r="857"/>
+    <row r="858"/>
+    <row r="859"/>
+    <row r="860"/>
+    <row r="861"/>
+    <row r="862"/>
+    <row r="863"/>
+    <row r="864"/>
+    <row r="865"/>
+    <row r="866"/>
+    <row r="867"/>
+    <row r="868"/>
+    <row r="869"/>
+    <row r="870"/>
+    <row r="871"/>
+    <row r="872"/>
+    <row r="873"/>
+    <row r="874"/>
+    <row r="875"/>
+    <row r="876"/>
+    <row r="877"/>
+    <row r="878"/>
+    <row r="879"/>
+    <row r="880"/>
+    <row r="881"/>
+    <row r="882"/>
+    <row r="883"/>
+    <row r="884"/>
+    <row r="885"/>
+    <row r="886"/>
+    <row r="887"/>
+    <row r="888"/>
+    <row r="889"/>
+    <row r="890"/>
+    <row r="891"/>
+    <row r="892"/>
+    <row r="893"/>
+    <row r="894"/>
+    <row r="895"/>
+    <row r="896"/>
+    <row r="897"/>
+    <row r="898"/>
+    <row r="899"/>
+    <row r="900"/>
+    <row r="901"/>
+    <row r="902"/>
+    <row r="903"/>
+    <row r="904"/>
+    <row r="905"/>
+    <row r="906"/>
+    <row r="907"/>
+    <row r="908"/>
+    <row r="909"/>
+    <row r="910"/>
+    <row r="911"/>
+    <row r="912"/>
+    <row r="913"/>
+    <row r="914"/>
+    <row r="915"/>
+    <row r="916"/>
+    <row r="917"/>
+    <row r="918"/>
+    <row r="919"/>
+    <row r="920"/>
+    <row r="921"/>
+    <row r="922"/>
+    <row r="923"/>
+    <row r="924"/>
+    <row r="925"/>
+    <row r="926"/>
+    <row r="927"/>
+    <row r="928"/>
+    <row r="929"/>
+    <row r="930"/>
+    <row r="931"/>
+    <row r="932"/>
+    <row r="933"/>
+    <row r="934"/>
+    <row r="935"/>
+    <row r="936"/>
+    <row r="937"/>
+    <row r="938"/>
+    <row r="939"/>
+    <row r="940"/>
+    <row r="941"/>
+    <row r="942"/>
+    <row r="943"/>
+    <row r="944"/>
+    <row r="945"/>
+    <row r="946"/>
+    <row r="947"/>
+    <row r="948"/>
+    <row r="949"/>
+    <row r="950"/>
+    <row r="951"/>
+    <row r="952"/>
+    <row r="953"/>
+    <row r="954"/>
+    <row r="955"/>
+    <row r="956"/>
+    <row r="957"/>
+    <row r="958"/>
+    <row r="959"/>
+    <row r="960"/>
+    <row r="961"/>
+    <row r="962"/>
+    <row r="963"/>
+    <row r="964"/>
+    <row r="965"/>
+    <row r="966"/>
+    <row r="967"/>
+    <row r="968"/>
+    <row r="969"/>
+    <row r="970"/>
+    <row r="971"/>
+    <row r="972"/>
+    <row r="973"/>
+    <row r="974"/>
+    <row r="975"/>
+    <row r="976"/>
+    <row r="977"/>
+    <row r="978"/>
+    <row r="979"/>
+    <row r="980"/>
+    <row r="981"/>
+    <row r="982"/>
+    <row r="983"/>
+    <row r="984"/>
+    <row r="985"/>
+    <row r="986"/>
+    <row r="987"/>
+    <row r="988"/>
+    <row r="989"/>
+    <row r="990"/>
+    <row r="991"/>
+    <row r="992"/>
+    <row r="993"/>
+    <row r="994"/>
+    <row r="995"/>
+    <row r="996"/>
+    <row r="997"/>
+    <row r="998"/>
+    <row r="999"/>
+    <row r="1000"/>
+    <row r="1001"/>
+    <row r="1002"/>
+    <row r="1003"/>
+    <row r="1004"/>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
+    <row r="1026"/>
+    <row r="1027"/>
+    <row r="1028"/>
+    <row r="1029"/>
+    <row r="1030"/>
+    <row r="1031"/>
+    <row r="1032"/>
+    <row r="1033"/>
+    <row r="1034"/>
+    <row r="1035"/>
+    <row r="1036"/>
+    <row r="1037"/>
+    <row r="1038"/>
+    <row r="1039"/>
+    <row r="1040"/>
+    <row r="1041"/>
+    <row r="1042"/>
+    <row r="1043"/>
+    <row r="1044"/>
+    <row r="1045"/>
+    <row r="1046"/>
+    <row r="1047"/>
+    <row r="1048"/>
+    <row r="1049"/>
+    <row r="1050"/>
+    <row r="1051"/>
+    <row r="1052"/>
+    <row r="1053"/>
+    <row r="1054"/>
+    <row r="1055"/>
+    <row r="1056"/>
+    <row r="1057"/>
+    <row r="1058"/>
+    <row r="1059"/>
+    <row r="1060"/>
+    <row r="1061"/>
+    <row r="1062"/>
+    <row r="1063"/>
+    <row r="1064"/>
+    <row r="1065"/>
+    <row r="1066"/>
+    <row r="1067"/>
+    <row r="1068"/>
+    <row r="1069"/>
+    <row r="1070"/>
+    <row r="1071"/>
+    <row r="1072"/>
+    <row r="1073"/>
+    <row r="1074"/>
+    <row r="1075"/>
+    <row r="1076"/>
+    <row r="1077"/>
+    <row r="1078"/>
+    <row r="1079"/>
+    <row r="1080"/>
+    <row r="1081"/>
+    <row r="1082"/>
+    <row r="1083"/>
+    <row r="1084"/>
+    <row r="1085"/>
+    <row r="1086"/>
+    <row r="1087"/>
+    <row r="1088"/>
+    <row r="1089"/>
+    <row r="1090"/>
+    <row r="1091"/>
+    <row r="1092"/>
+    <row r="1093"/>
+    <row r="1094"/>
+    <row r="1095"/>
+    <row r="1096"/>
+    <row r="1097"/>
+    <row r="1098"/>
+    <row r="1099"/>
+    <row r="1100"/>
+    <row r="1101"/>
+    <row r="1102"/>
+    <row r="1103"/>
+    <row r="1104"/>
+    <row r="1105"/>
+    <row r="1106"/>
+    <row r="1107"/>
+    <row r="1108"/>
+    <row r="1109"/>
+    <row r="1110"/>
+    <row r="1111"/>
+    <row r="1112"/>
+    <row r="1113"/>
+    <row r="1114"/>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B807" t="n">
+      <c r="B1115" t="n">
         <v>0</v>
       </c>
-      <c r="C807" t="n">
+      <c r="C1115" t="n">
         <v>286.32</v>
       </c>
-      <c r="D807" t="n">
+      <c r="D1115" t="n">
         <v>0</v>
       </c>
-      <c r="E807" t="n">
+      <c r="E1115" t="n">
         <v>0</v>
       </c>
-      <c r="F807" t="n">
+      <c r="F1115" t="n">
         <v>286.32</v>
       </c>
-      <c r="G807" t="n">
+      <c r="G1115" t="n">
         <v>-286.32</v>
       </c>
-      <c r="H807" t="inlineStr">
+      <c r="H1115" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="808">
-      <c r="A808" t="inlineStr">
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B808" t="n">
+      <c r="B1116" t="n">
         <v>0</v>
       </c>
-      <c r="C808" t="n">
+      <c r="C1116" t="n">
         <v>241.36</v>
       </c>
-      <c r="D808" t="n">
+      <c r="D1116" t="n">
         <v>0</v>
       </c>
-      <c r="E808" t="n">
+      <c r="E1116" t="n">
         <v>0</v>
       </c>
-      <c r="F808" t="n">
+      <c r="F1116" t="n">
         <v>241.36</v>
       </c>
-      <c r="G808" t="n">
+      <c r="G1116" t="n">
         <v>-241.36</v>
       </c>
-      <c r="H808" t="inlineStr">
+      <c r="H1116" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="809">
-      <c r="A809" t="inlineStr">
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B809" t="n">
+      <c r="B1117" t="n">
         <v>1500</v>
       </c>
-      <c r="C809" t="n">
-        <v>5020.3</v>
-      </c>
-      <c r="D809" t="n">
+      <c r="C1117" t="n">
+        <v>4986.950000000001</v>
+      </c>
+      <c r="D1117" t="n">
         <v>3671.87</v>
       </c>
-      <c r="E809" t="n">
-        <v>199.9</v>
-      </c>
-      <c r="F809" t="n">
+      <c r="E1117" t="n">
+        <v>166.55</v>
+      </c>
+      <c r="F1117" t="n">
         <v>400.38</v>
       </c>
-      <c r="G809" t="n">
-        <v>-3520.3</v>
-      </c>
-      <c r="H809" t="inlineStr">
+      <c r="G1117" t="n">
+        <v>-3486.950000000001</v>
+      </c>
+      <c r="H1117" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="810">
-      <c r="A810" t="inlineStr">
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B810" t="n">
+      <c r="B1118" t="n">
         <v>700</v>
       </c>
-      <c r="C810" t="n">
-        <v>1645.89</v>
-      </c>
-      <c r="D810" t="n">
+      <c r="C1118" t="n">
+        <v>2759.36</v>
+      </c>
+      <c r="D1118" t="n">
         <v>1238.48</v>
       </c>
-      <c r="E810" t="n">
+      <c r="E1118" t="n">
+        <v>428.06</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>565.28</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>-2059.36</v>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>NEG</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B1119" t="n">
         <v>0</v>
       </c>
-      <c r="F810" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="G810" t="n">
-        <v>-945.8900000000001</v>
-      </c>
-      <c r="H810" t="inlineStr">
+      <c r="C1119" t="n">
+        <v>460.34</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>460.34</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1119" t="n">
+        <v>-460.34</v>
+      </c>
+      <c r="H1119" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="811">
-      <c r="A811" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B811" t="n">
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B1120" t="n">
         <v>0</v>
       </c>
-      <c r="C811" t="n">
-        <v>460.34</v>
-      </c>
-      <c r="D811" t="n">
-        <v>460.34</v>
-      </c>
-      <c r="E811" t="n">
+      <c r="C1120" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="E1120" t="n">
         <v>0</v>
       </c>
-      <c r="F811" t="n">
+      <c r="F1120" t="n">
         <v>0</v>
       </c>
-      <c r="G811" t="n">
-        <v>-460.34</v>
-      </c>
-      <c r="H811" t="inlineStr">
+      <c r="G1120" t="n">
+        <v>-360.34</v>
+      </c>
+      <c r="H1120" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="812">
-      <c r="A812" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B812" t="n">
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B1121" t="n">
         <v>0</v>
       </c>
-      <c r="C812" t="n">
+      <c r="C1121" t="n">
         <v>360.34</v>
       </c>
-      <c r="D812" t="n">
+      <c r="D1121" t="n">
         <v>360.34</v>
       </c>
-      <c r="E812" t="n">
+      <c r="E1121" t="n">
         <v>0</v>
       </c>
-      <c r="F812" t="n">
+      <c r="F1121" t="n">
         <v>0</v>
       </c>
-      <c r="G812" t="n">
+      <c r="G1121" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H812" t="inlineStr">
+      <c r="H1121" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="813">
-      <c r="A813" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B813" t="n">
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B1122" t="n">
         <v>0</v>
       </c>
-      <c r="C813" t="n">
+      <c r="C1122" t="n">
         <v>360.34</v>
       </c>
-      <c r="D813" t="n">
+      <c r="D1122" t="n">
         <v>360.34</v>
       </c>
-      <c r="E813" t="n">
+      <c r="E1122" t="n">
         <v>0</v>
       </c>
-      <c r="F813" t="n">
+      <c r="F1122" t="n">
         <v>0</v>
       </c>
-      <c r="G813" t="n">
+      <c r="G1122" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H813" t="inlineStr">
+      <c r="H1122" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="814">
-      <c r="A814" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B814" t="n">
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B1123" t="n">
         <v>0</v>
       </c>
-      <c r="C814" t="n">
+      <c r="C1123" t="n">
         <v>360.34</v>
       </c>
-      <c r="D814" t="n">
+      <c r="D1123" t="n">
         <v>360.34</v>
       </c>
-      <c r="E814" t="n">
+      <c r="E1123" t="n">
         <v>0</v>
       </c>
-      <c r="F814" t="n">
+      <c r="F1123" t="n">
         <v>0</v>
       </c>
-      <c r="G814" t="n">
+      <c r="G1123" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H814" t="inlineStr">
+      <c r="H1123" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="815">
-      <c r="A815" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B815" t="n">
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B1124" t="n">
         <v>0</v>
       </c>
-      <c r="C815" t="n">
+      <c r="C1124" t="n">
         <v>360.34</v>
       </c>
-      <c r="D815" t="n">
+      <c r="D1124" t="n">
         <v>360.34</v>
       </c>
-      <c r="E815" t="n">
+      <c r="E1124" t="n">
         <v>0</v>
       </c>
-      <c r="F815" t="n">
+      <c r="F1124" t="n">
         <v>0</v>
       </c>
-      <c r="G815" t="n">
+      <c r="G1124" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H815" t="inlineStr">
+      <c r="H1124" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="816">
-      <c r="A816" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B816" t="n">
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B1125" t="n">
         <v>0</v>
       </c>
-      <c r="C816" t="n">
-        <v>360.34</v>
-      </c>
-      <c r="D816" t="n">
-        <v>360.34</v>
-      </c>
-      <c r="E816" t="n">
+      <c r="C1125" t="n">
+        <v>308.46</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>308.46</v>
+      </c>
+      <c r="E1125" t="n">
         <v>0</v>
       </c>
-      <c r="F816" t="n">
+      <c r="F1125" t="n">
         <v>0</v>
       </c>
-      <c r="G816" t="n">
-        <v>-360.34</v>
-      </c>
-      <c r="H816" t="inlineStr">
+      <c r="G1125" t="n">
+        <v>-308.46</v>
+      </c>
+      <c r="H1125" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="817">
-      <c r="A817" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="B817" t="n">
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B1126" t="n">
         <v>0</v>
       </c>
-      <c r="C817" t="n">
+      <c r="C1126" t="n">
         <v>308.46</v>
       </c>
-      <c r="D817" t="n">
+      <c r="D1126" t="n">
         <v>308.46</v>
       </c>
-      <c r="E817" t="n">
+      <c r="E1126" t="n">
         <v>0</v>
       </c>
-      <c r="F817" t="n">
+      <c r="F1126" t="n">
         <v>0</v>
       </c>
-      <c r="G817" t="n">
+      <c r="G1126" t="n">
         <v>-308.46</v>
       </c>
-      <c r="H817" t="inlineStr">
+      <c r="H1126" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="818">
-      <c r="A818" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B818" t="n">
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="B1127" t="n">
         <v>0</v>
       </c>
-      <c r="C818" t="n">
-        <v>308.46</v>
-      </c>
-      <c r="D818" t="n">
-        <v>308.46</v>
-      </c>
-      <c r="E818" t="n">
+      <c r="C1127" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>174.83</v>
+      </c>
+      <c r="E1127" t="n">
         <v>0</v>
       </c>
-      <c r="F818" t="n">
+      <c r="F1127" t="n">
         <v>0</v>
       </c>
-      <c r="G818" t="n">
-        <v>-308.46</v>
-      </c>
-      <c r="H818" t="inlineStr">
+      <c r="G1127" t="n">
+        <v>-174.83</v>
+      </c>
+      <c r="H1127" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="819">
-      <c r="A819" t="inlineStr">
-        <is>
-          <t>2027-01</t>
-        </is>
-      </c>
-      <c r="B819" t="n">
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="B1128" t="n">
         <v>0</v>
       </c>
-      <c r="C819" t="n">
+      <c r="C1128" t="n">
         <v>174.83</v>
       </c>
-      <c r="D819" t="n">
+      <c r="D1128" t="n">
         <v>174.83</v>
       </c>
-      <c r="E819" t="n">
+      <c r="E1128" t="n">
         <v>0</v>
       </c>
-      <c r="F819" t="n">
+      <c r="F1128" t="n">
         <v>0</v>
       </c>
-      <c r="G819" t="n">
+      <c r="G1128" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H819" t="inlineStr">
-        <is>
-          <t>NEG</t>
-        </is>
-      </c>
-    </row>
-    <row r="820">
-      <c r="A820" t="inlineStr">
-        <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="B820" t="n">
-        <v>0</v>
-      </c>
-      <c r="C820" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="D820" t="n">
-        <v>174.83</v>
-      </c>
-      <c r="E820" t="n">
-        <v>0</v>
-      </c>
-      <c r="F820" t="n">
-        <v>0</v>
-      </c>
-      <c r="G820" t="n">
-        <v>-174.83</v>
-      </c>
-      <c r="H820" t="inlineStr">
+      <c r="H1128" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>

--- a/financas_casa.xlsx
+++ b/financas_casa.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1105,6 +1105,98 @@
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Laser</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>🎮 Lazer</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Despesa</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>323.11</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Rodizio de petiscos no dona branca</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Transacao_Lazer_Laser_2026-04-13_18-43-42.jpeg</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Trabalho nas eleições</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>💰 Freelance</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Ambos</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Trabalho nas eleições</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
@@ -5771,7 +5863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1128"/>
+  <dimension ref="A1:H1156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5966,1520 +6058,421 @@
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="5" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
-    <row r="1001"/>
-    <row r="1002"/>
-    <row r="1003"/>
-    <row r="1004"/>
-    <row r="1005"/>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
-    <row r="1022"/>
-    <row r="1023"/>
-    <row r="1024"/>
-    <row r="1025"/>
-    <row r="1026"/>
-    <row r="1027"/>
-    <row r="1028"/>
-    <row r="1029"/>
-    <row r="1030"/>
-    <row r="1031"/>
-    <row r="1032"/>
-    <row r="1033"/>
-    <row r="1034"/>
-    <row r="1035"/>
-    <row r="1036"/>
-    <row r="1037"/>
-    <row r="1038"/>
-    <row r="1039"/>
-    <row r="1040"/>
-    <row r="1041"/>
-    <row r="1042"/>
-    <row r="1043"/>
-    <row r="1044"/>
-    <row r="1045"/>
-    <row r="1046"/>
-    <row r="1047"/>
-    <row r="1048"/>
-    <row r="1049"/>
-    <row r="1050"/>
-    <row r="1051"/>
-    <row r="1052"/>
-    <row r="1053"/>
-    <row r="1054"/>
-    <row r="1055"/>
-    <row r="1056"/>
-    <row r="1057"/>
-    <row r="1058"/>
-    <row r="1059"/>
-    <row r="1060"/>
-    <row r="1061"/>
-    <row r="1062"/>
-    <row r="1063"/>
-    <row r="1064"/>
-    <row r="1065"/>
-    <row r="1066"/>
-    <row r="1067"/>
-    <row r="1068"/>
-    <row r="1069"/>
-    <row r="1070"/>
-    <row r="1071"/>
-    <row r="1072"/>
-    <row r="1073"/>
-    <row r="1074"/>
-    <row r="1075"/>
-    <row r="1076"/>
-    <row r="1077"/>
-    <row r="1078"/>
-    <row r="1079"/>
-    <row r="1080"/>
-    <row r="1081"/>
-    <row r="1082"/>
-    <row r="1083"/>
-    <row r="1084"/>
-    <row r="1085"/>
-    <row r="1086"/>
-    <row r="1087"/>
-    <row r="1088"/>
-    <row r="1089"/>
-    <row r="1090"/>
-    <row r="1091"/>
-    <row r="1092"/>
-    <row r="1093"/>
-    <row r="1094"/>
-    <row r="1095"/>
-    <row r="1096"/>
-    <row r="1097"/>
-    <row r="1098"/>
-    <row r="1099"/>
-    <row r="1100"/>
-    <row r="1101"/>
-    <row r="1102"/>
-    <row r="1103"/>
-    <row r="1104"/>
-    <row r="1105"/>
-    <row r="1106"/>
-    <row r="1107"/>
-    <row r="1108"/>
-    <row r="1109"/>
-    <row r="1110"/>
-    <row r="1111"/>
-    <row r="1112"/>
-    <row r="1113"/>
-    <row r="1114"/>
-    <row r="1115">
-      <c r="A1115" t="inlineStr">
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B1115" t="n">
+      <c r="B1143" t="n">
         <v>0</v>
       </c>
-      <c r="C1115" t="n">
+      <c r="C1143" t="n">
         <v>286.32</v>
       </c>
-      <c r="D1115" t="n">
+      <c r="D1143" t="n">
         <v>0</v>
       </c>
-      <c r="E1115" t="n">
+      <c r="E1143" t="n">
         <v>0</v>
       </c>
-      <c r="F1115" t="n">
+      <c r="F1143" t="n">
         <v>286.32</v>
       </c>
-      <c r="G1115" t="n">
+      <c r="G1143" t="n">
         <v>-286.32</v>
       </c>
-      <c r="H1115" t="inlineStr">
+      <c r="H1143" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1116">
-      <c r="A1116" t="inlineStr">
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B1116" t="n">
+      <c r="B1144" t="n">
         <v>0</v>
       </c>
-      <c r="C1116" t="n">
+      <c r="C1144" t="n">
         <v>241.36</v>
       </c>
-      <c r="D1116" t="n">
+      <c r="D1144" t="n">
         <v>0</v>
       </c>
-      <c r="E1116" t="n">
+      <c r="E1144" t="n">
         <v>0</v>
       </c>
-      <c r="F1116" t="n">
+      <c r="F1144" t="n">
         <v>241.36</v>
       </c>
-      <c r="G1116" t="n">
+      <c r="G1144" t="n">
         <v>-241.36</v>
       </c>
-      <c r="H1116" t="inlineStr">
+      <c r="H1144" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1117">
-      <c r="A1117" t="inlineStr">
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B1117" t="n">
+      <c r="B1145" t="n">
         <v>1500</v>
       </c>
-      <c r="C1117" t="n">
+      <c r="C1145" t="n">
         <v>4986.950000000001</v>
       </c>
-      <c r="D1117" t="n">
+      <c r="D1145" t="n">
         <v>3671.87</v>
       </c>
-      <c r="E1117" t="n">
+      <c r="E1145" t="n">
         <v>166.55</v>
       </c>
-      <c r="F1117" t="n">
+      <c r="F1145" t="n">
         <v>400.38</v>
       </c>
-      <c r="G1117" t="n">
+      <c r="G1145" t="n">
         <v>-3486.950000000001</v>
       </c>
-      <c r="H1117" t="inlineStr">
+      <c r="H1145" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1118">
-      <c r="A1118" t="inlineStr">
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B1118" t="n">
-        <v>700</v>
-      </c>
-      <c r="C1118" t="n">
-        <v>2759.36</v>
-      </c>
-      <c r="D1118" t="n">
+      <c r="B1146" t="n">
+        <v>900</v>
+      </c>
+      <c r="C1146" t="n">
+        <v>3082.47</v>
+      </c>
+      <c r="D1146" t="n">
         <v>1238.48</v>
       </c>
-      <c r="E1118" t="n">
+      <c r="E1146" t="n">
         <v>428.06</v>
       </c>
-      <c r="F1118" t="n">
+      <c r="F1146" t="n">
         <v>565.28</v>
       </c>
-      <c r="G1118" t="n">
-        <v>-2059.36</v>
-      </c>
-      <c r="H1118" t="inlineStr">
+      <c r="G1146" t="n">
+        <v>-2182.47</v>
+      </c>
+      <c r="H1146" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1119">
-      <c r="A1119" t="inlineStr">
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B1119" t="n">
+      <c r="B1147" t="n">
         <v>0</v>
       </c>
-      <c r="C1119" t="n">
+      <c r="C1147" t="n">
         <v>460.34</v>
       </c>
-      <c r="D1119" t="n">
+      <c r="D1147" t="n">
         <v>460.34</v>
       </c>
-      <c r="E1119" t="n">
+      <c r="E1147" t="n">
         <v>0</v>
       </c>
-      <c r="F1119" t="n">
+      <c r="F1147" t="n">
         <v>0</v>
       </c>
-      <c r="G1119" t="n">
+      <c r="G1147" t="n">
         <v>-460.34</v>
       </c>
-      <c r="H1119" t="inlineStr">
+      <c r="H1147" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1120">
-      <c r="A1120" t="inlineStr">
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B1120" t="n">
+      <c r="B1148" t="n">
         <v>0</v>
       </c>
-      <c r="C1120" t="n">
+      <c r="C1148" t="n">
         <v>360.34</v>
       </c>
-      <c r="D1120" t="n">
+      <c r="D1148" t="n">
         <v>360.34</v>
       </c>
-      <c r="E1120" t="n">
+      <c r="E1148" t="n">
         <v>0</v>
       </c>
-      <c r="F1120" t="n">
+      <c r="F1148" t="n">
         <v>0</v>
       </c>
-      <c r="G1120" t="n">
+      <c r="G1148" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H1120" t="inlineStr">
+      <c r="H1148" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1121">
-      <c r="A1121" t="inlineStr">
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B1121" t="n">
+      <c r="B1149" t="n">
         <v>0</v>
       </c>
-      <c r="C1121" t="n">
+      <c r="C1149" t="n">
         <v>360.34</v>
       </c>
-      <c r="D1121" t="n">
+      <c r="D1149" t="n">
         <v>360.34</v>
       </c>
-      <c r="E1121" t="n">
+      <c r="E1149" t="n">
         <v>0</v>
       </c>
-      <c r="F1121" t="n">
+      <c r="F1149" t="n">
         <v>0</v>
       </c>
-      <c r="G1121" t="n">
+      <c r="G1149" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H1121" t="inlineStr">
+      <c r="H1149" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1122">
-      <c r="A1122" t="inlineStr">
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B1122" t="n">
+      <c r="B1150" t="n">
         <v>0</v>
       </c>
-      <c r="C1122" t="n">
+      <c r="C1150" t="n">
         <v>360.34</v>
       </c>
-      <c r="D1122" t="n">
+      <c r="D1150" t="n">
         <v>360.34</v>
       </c>
-      <c r="E1122" t="n">
+      <c r="E1150" t="n">
         <v>0</v>
       </c>
-      <c r="F1122" t="n">
+      <c r="F1150" t="n">
         <v>0</v>
       </c>
-      <c r="G1122" t="n">
+      <c r="G1150" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H1122" t="inlineStr">
+      <c r="H1150" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1123">
-      <c r="A1123" t="inlineStr">
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="B1123" t="n">
+      <c r="B1151" t="n">
         <v>0</v>
       </c>
-      <c r="C1123" t="n">
+      <c r="C1151" t="n">
         <v>360.34</v>
       </c>
-      <c r="D1123" t="n">
+      <c r="D1151" t="n">
         <v>360.34</v>
       </c>
-      <c r="E1123" t="n">
+      <c r="E1151" t="n">
         <v>0</v>
       </c>
-      <c r="F1123" t="n">
+      <c r="F1151" t="n">
         <v>0</v>
       </c>
-      <c r="G1123" t="n">
+      <c r="G1151" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H1123" t="inlineStr">
+      <c r="H1151" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1124">
-      <c r="A1124" t="inlineStr">
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="B1124" t="n">
+      <c r="B1152" t="n">
         <v>0</v>
       </c>
-      <c r="C1124" t="n">
+      <c r="C1152" t="n">
         <v>360.34</v>
       </c>
-      <c r="D1124" t="n">
+      <c r="D1152" t="n">
         <v>360.34</v>
       </c>
-      <c r="E1124" t="n">
+      <c r="E1152" t="n">
         <v>0</v>
       </c>
-      <c r="F1124" t="n">
+      <c r="F1152" t="n">
         <v>0</v>
       </c>
-      <c r="G1124" t="n">
+      <c r="G1152" t="n">
         <v>-360.34</v>
       </c>
-      <c r="H1124" t="inlineStr">
+      <c r="H1152" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1125">
-      <c r="A1125" t="inlineStr">
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
         <is>
           <t>2026-11</t>
         </is>
       </c>
-      <c r="B1125" t="n">
+      <c r="B1153" t="n">
         <v>0</v>
       </c>
-      <c r="C1125" t="n">
+      <c r="C1153" t="n">
         <v>308.46</v>
       </c>
-      <c r="D1125" t="n">
+      <c r="D1153" t="n">
         <v>308.46</v>
       </c>
-      <c r="E1125" t="n">
+      <c r="E1153" t="n">
         <v>0</v>
       </c>
-      <c r="F1125" t="n">
+      <c r="F1153" t="n">
         <v>0</v>
       </c>
-      <c r="G1125" t="n">
+      <c r="G1153" t="n">
         <v>-308.46</v>
       </c>
-      <c r="H1125" t="inlineStr">
+      <c r="H1153" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1126">
-      <c r="A1126" t="inlineStr">
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
         <is>
           <t>2026-12</t>
         </is>
       </c>
-      <c r="B1126" t="n">
+      <c r="B1154" t="n">
         <v>0</v>
       </c>
-      <c r="C1126" t="n">
+      <c r="C1154" t="n">
         <v>308.46</v>
       </c>
-      <c r="D1126" t="n">
+      <c r="D1154" t="n">
         <v>308.46</v>
       </c>
-      <c r="E1126" t="n">
+      <c r="E1154" t="n">
         <v>0</v>
       </c>
-      <c r="F1126" t="n">
+      <c r="F1154" t="n">
         <v>0</v>
       </c>
-      <c r="G1126" t="n">
+      <c r="G1154" t="n">
         <v>-308.46</v>
       </c>
-      <c r="H1126" t="inlineStr">
+      <c r="H1154" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1127">
-      <c r="A1127" t="inlineStr">
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
         <is>
           <t>2027-01</t>
         </is>
       </c>
-      <c r="B1127" t="n">
+      <c r="B1155" t="n">
         <v>0</v>
       </c>
-      <c r="C1127" t="n">
+      <c r="C1155" t="n">
         <v>174.83</v>
       </c>
-      <c r="D1127" t="n">
+      <c r="D1155" t="n">
         <v>174.83</v>
       </c>
-      <c r="E1127" t="n">
+      <c r="E1155" t="n">
         <v>0</v>
       </c>
-      <c r="F1127" t="n">
+      <c r="F1155" t="n">
         <v>0</v>
       </c>
-      <c r="G1127" t="n">
+      <c r="G1155" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H1127" t="inlineStr">
+      <c r="H1155" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
       </c>
     </row>
-    <row r="1128">
-      <c r="A1128" t="inlineStr">
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
         <is>
           <t>2027-02</t>
         </is>
       </c>
-      <c r="B1128" t="n">
+      <c r="B1156" t="n">
         <v>0</v>
       </c>
-      <c r="C1128" t="n">
+      <c r="C1156" t="n">
         <v>174.83</v>
       </c>
-      <c r="D1128" t="n">
+      <c r="D1156" t="n">
         <v>174.83</v>
       </c>
-      <c r="E1128" t="n">
+      <c r="E1156" t="n">
         <v>0</v>
       </c>
-      <c r="F1128" t="n">
+      <c r="F1156" t="n">
         <v>0</v>
       </c>
-      <c r="G1128" t="n">
+      <c r="G1156" t="n">
         <v>-174.83</v>
       </c>
-      <c r="H1128" t="inlineStr">
+      <c r="H1156" t="inlineStr">
         <is>
           <t>NEG</t>
         </is>
